--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/observations-summary.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="78">
   <si>
     <t>Profile</t>
   </si>
@@ -71,34 +71,46 @@
     <t>optional</t>
   </si>
   <si>
+    <t>jp-observation-dentaloral-ecs</t>
+  </si>
+  <si>
+    <t>JP Core Observation DentalOral eCS Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#exam, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-04</t>
+  </si>
+  <si>
+    <t>null#57133-1</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>CodeableConcept</t>
+  </si>
+  <si>
     <t>jp-observation-dentaloral-missingtoothcondition</t>
   </si>
   <si>
     <t>JP Core Observation DentalOral Missing Tooth Condition Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-03</t>
+    <t>JP Core Simple Observation Category CodeSystem#exam, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-03</t>
   </si>
   <si>
     <t>null#54570-7</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>CodeableConcept</t>
-  </si>
-  <si>
     <t>jp-observation-dentaloral-toothexistence</t>
   </si>
   <si>
     <t>JP Core Observation DentalOral Tooth Existence Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-01</t>
+    <t>JP Core Simple Observation Category CodeSystem#exam, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-01</t>
   </si>
   <si>
     <t>jp-observation-dentaloral-toothtreatmentcondition</t>
@@ -107,7 +119,7 @@
     <t>JP Core Observation DentalOral Tooth Treatment Condition Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-02</t>
+    <t>JP Core Simple Observation Category CodeSystem#exam, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-02</t>
   </si>
   <si>
     <t>jp-observation-electrocardiogram</t>
@@ -367,7 +379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -489,7 +501,7 @@
         <v>14</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>23</v>
@@ -512,19 +524,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>22</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>23</v>
@@ -547,28 +559,28 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>18</v>
@@ -582,28 +594,28 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="C7" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="C7" t="s" s="2">
+      <c r="D7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="F7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="G7" t="s" s="2">
-        <v>41</v>
-      </c>
       <c r="H7" t="s" s="2">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -617,28 +629,28 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="D8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="C8" t="s" s="2">
+      <c r="G8" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s" s="2">
+      <c r="H8" t="s" s="2">
         <v>46</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -652,28 +664,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="C9" t="s" s="2">
+      <c r="G9" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s" s="2">
+      <c r="H9" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -699,16 +711,16 @@
         <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="F10" t="s" s="2">
-        <v>57</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>18</v>
@@ -722,28 +734,28 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="C11" t="s" s="2">
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s" s="2">
+      <c r="F11" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="F11" t="s" s="2">
-        <v>23</v>
-      </c>
       <c r="G11" t="s" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -757,13 +769,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="B12" t="s" s="2">
+      <c r="C12" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>60</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>14</v>
@@ -778,7 +790,7 @@
         <v>24</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>18</v>
@@ -792,28 +804,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="H13" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -848,15 +860,50 @@
         <v>16</v>
       </c>
       <c r="H14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H15" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="I14" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K14" t="s" s="2">
+      <c r="I15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K15" t="s" s="2">
         <v>14</v>
       </c>
     </row>
